--- a/artfynd/A 56873-2025 artfynd.xlsx
+++ b/artfynd/A 56873-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133706599</v>
+        <v>133706573</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446796</v>
+        <v>446844</v>
       </c>
       <c r="R3" t="n">
-        <v>6997286</v>
+        <v>6997413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133706603</v>
+        <v>133706610</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>91956</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446807</v>
+        <v>446941</v>
       </c>
       <c r="R4" t="n">
-        <v>6997279</v>
+        <v>6997191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133706604</v>
+        <v>133706557</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446725</v>
+        <v>446868</v>
       </c>
       <c r="R5" t="n">
-        <v>6997251</v>
+        <v>6997390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133706597</v>
+        <v>133706594</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446792</v>
+        <v>446798</v>
       </c>
       <c r="R6" t="n">
-        <v>6997319</v>
+        <v>6997394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133706573</v>
+        <v>133706590</v>
       </c>
       <c r="B7" t="n">
         <v>79359</v>
@@ -1265,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446844</v>
+        <v>446811</v>
       </c>
       <c r="R7" t="n">
-        <v>6997413</v>
+        <v>6997443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133706610</v>
+        <v>133706582</v>
       </c>
       <c r="B8" t="n">
-        <v>91956</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446941</v>
+        <v>446833</v>
       </c>
       <c r="R8" t="n">
-        <v>6997191</v>
+        <v>6997476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133706577</v>
+        <v>133706591</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446838</v>
+        <v>446806</v>
       </c>
       <c r="R9" t="n">
-        <v>6997451</v>
+        <v>6997430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gammalt troligt bo av tretåig hackspett, ca 1,4m upp i tajgagrantickerötad granhögstubbe</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133706594</v>
+        <v>133706579</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>91960</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446798</v>
+        <v>446826</v>
       </c>
       <c r="R10" t="n">
-        <v>6997394</v>
+        <v>6997453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133706557</v>
+        <v>133706599</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446868</v>
+        <v>446796</v>
       </c>
       <c r="R11" t="n">
-        <v>6997390</v>
+        <v>6997286</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1718,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133706601</v>
+        <v>133706597</v>
       </c>
       <c r="B12" t="n">
         <v>57975</v>
@@ -1805,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446800</v>
+        <v>446792</v>
       </c>
       <c r="R12" t="n">
-        <v>6997283</v>
+        <v>6997319</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,12 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133706587</v>
+        <v>133706603</v>
       </c>
       <c r="B13" t="n">
         <v>57975</v>
@@ -1917,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446795</v>
+        <v>446807</v>
       </c>
       <c r="R13" t="n">
-        <v>6997454</v>
+        <v>6997279</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,12 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133706602</v>
+        <v>133706604</v>
       </c>
       <c r="B14" t="n">
         <v>57975</v>
@@ -2029,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446805</v>
+        <v>446725</v>
       </c>
       <c r="R14" t="n">
-        <v>6997283</v>
+        <v>6997251</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2074,12 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133706590</v>
+        <v>133706577</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2141,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446811</v>
+        <v>446838</v>
       </c>
       <c r="R15" t="n">
-        <v>6997443</v>
+        <v>6997451</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2186,7 +2166,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gammalt troligt bo av tretåig hackspett, ca 1,4m upp i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,7 +2198,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133706588</v>
+        <v>133706601</v>
       </c>
       <c r="B16" t="n">
         <v>57975</v>
@@ -2248,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446805</v>
+        <v>446800</v>
       </c>
       <c r="R16" t="n">
-        <v>6997442</v>
+        <v>6997283</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2293,12 +2278,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133706582</v>
+        <v>133706587</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2360,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446833</v>
+        <v>446795</v>
       </c>
       <c r="R17" t="n">
-        <v>6997476</v>
+        <v>6997454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2405,7 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,7 +2422,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133706585</v>
+        <v>133706602</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2467,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446816</v>
+        <v>446805</v>
       </c>
       <c r="R18" t="n">
-        <v>6997484</v>
+        <v>6997283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2544,7 +2534,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133706606</v>
+        <v>133706588</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2579,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446774</v>
+        <v>446805</v>
       </c>
       <c r="R19" t="n">
-        <v>6997294</v>
+        <v>6997442</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2624,7 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2656,7 +2646,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133706607</v>
+        <v>133706585</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2691,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446894</v>
+        <v>446816</v>
       </c>
       <c r="R20" t="n">
-        <v>6997185</v>
+        <v>6997484</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2726,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2736,12 +2726,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133706591</v>
+        <v>133706607</v>
       </c>
       <c r="B21" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2779,21 +2769,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2803,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446806</v>
+        <v>446894</v>
       </c>
       <c r="R21" t="n">
-        <v>6997430</v>
+        <v>6997185</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2838,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2848,7 +2838,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,7 +2870,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133706605</v>
+        <v>133706606</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -2910,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446755</v>
+        <v>446774</v>
       </c>
       <c r="R22" t="n">
-        <v>6997227</v>
+        <v>6997294</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,7 +2940,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2955,7 +2950,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2987,7 +2982,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133706571</v>
+        <v>133706605</v>
       </c>
       <c r="B23" t="n">
         <v>57975</v>
@@ -3022,10 +3017,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446829</v>
+        <v>446755</v>
       </c>
       <c r="R23" t="n">
-        <v>6997424</v>
+        <v>6997227</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3057,7 +3052,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3067,12 +3062,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3099,10 +3094,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133706579</v>
+        <v>133706571</v>
       </c>
       <c r="B24" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,21 +3105,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3134,10 +3129,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446826</v>
+        <v>446829</v>
       </c>
       <c r="R24" t="n">
-        <v>6997453</v>
+        <v>6997424</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3164,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3179,7 +3174,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 56873-2025 artfynd.xlsx
+++ b/artfynd/A 56873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133706576</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133706573</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133706610</v>
       </c>
       <c r="B4" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133706557</v>
+        <v>133706594</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446868</v>
+        <v>446798</v>
       </c>
       <c r="R5" t="n">
-        <v>6997390</v>
+        <v>6997394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133706594</v>
+        <v>133706557</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446798</v>
+        <v>446868</v>
       </c>
       <c r="R6" t="n">
-        <v>6997394</v>
+        <v>6997390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>133706590</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>133706582</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>133706591</v>
       </c>
       <c r="B9" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>133706579</v>
       </c>
       <c r="B10" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133706597</v>
+        <v>133706603</v>
       </c>
       <c r="B12" t="n">
         <v>57975</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446792</v>
+        <v>446807</v>
       </c>
       <c r="R12" t="n">
-        <v>6997319</v>
+        <v>6997279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133706603</v>
+        <v>133706604</v>
       </c>
       <c r="B13" t="n">
         <v>57975</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446807</v>
+        <v>446725</v>
       </c>
       <c r="R13" t="n">
-        <v>6997279</v>
+        <v>6997251</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133706604</v>
+        <v>133706597</v>
       </c>
       <c r="B14" t="n">
         <v>57975</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446725</v>
+        <v>446792</v>
       </c>
       <c r="R14" t="n">
-        <v>6997251</v>
+        <v>6997319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2758,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133706607</v>
+        <v>133706606</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446894</v>
+        <v>446774</v>
       </c>
       <c r="R21" t="n">
-        <v>6997185</v>
+        <v>6997294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2870,7 +2870,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133706606</v>
+        <v>133706607</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446774</v>
+        <v>446894</v>
       </c>
       <c r="R22" t="n">
-        <v>6997294</v>
+        <v>6997185</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">

--- a/artfynd/A 56873-2025 artfynd.xlsx
+++ b/artfynd/A 56873-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133706576</v>
+        <v>133706610</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446847</v>
+        <v>446941</v>
       </c>
       <c r="R2" t="n">
-        <v>6997329</v>
+        <v>6997191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133706573</v>
+        <v>133706579</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446844</v>
+        <v>446826</v>
       </c>
       <c r="R3" t="n">
-        <v>6997413</v>
+        <v>6997453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133706610</v>
+        <v>133706591</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446941</v>
+        <v>446806</v>
       </c>
       <c r="R4" t="n">
-        <v>6997191</v>
+        <v>6997430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133706594</v>
+        <v>133706557</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446798</v>
+        <v>446868</v>
       </c>
       <c r="R5" t="n">
-        <v>6997394</v>
+        <v>6997390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133706557</v>
+        <v>133706573</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446868</v>
+        <v>446844</v>
       </c>
       <c r="R6" t="n">
-        <v>6997390</v>
+        <v>6997413</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133706590</v>
+        <v>133706576</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446811</v>
+        <v>446847</v>
       </c>
       <c r="R7" t="n">
-        <v>6997443</v>
+        <v>6997329</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,11 +1320,11 @@
         <v>133706582</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133706591</v>
+        <v>133706590</v>
       </c>
       <c r="B9" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446806</v>
+        <v>446811</v>
       </c>
       <c r="R9" t="n">
-        <v>6997430</v>
+        <v>6997443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133706579</v>
+        <v>133706594</v>
       </c>
       <c r="B10" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446826</v>
+        <v>446798</v>
       </c>
       <c r="R10" t="n">
-        <v>6997453</v>
+        <v>6997394</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133706599</v>
+        <v>133706561</v>
       </c>
       <c r="B11" t="n">
         <v>57975</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446796</v>
+        <v>446865</v>
       </c>
       <c r="R11" t="n">
-        <v>6997286</v>
+        <v>6997453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133706603</v>
+        <v>133706571</v>
       </c>
       <c r="B12" t="n">
         <v>57975</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446807</v>
+        <v>446829</v>
       </c>
       <c r="R12" t="n">
-        <v>6997279</v>
+        <v>6997424</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133706604</v>
+        <v>133706577</v>
       </c>
       <c r="B13" t="n">
         <v>57975</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446725</v>
+        <v>446838</v>
       </c>
       <c r="R13" t="n">
-        <v>6997251</v>
+        <v>6997451</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Gammalt troligt bo av tretåig hackspett, ca 1,4m upp i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133706597</v>
+        <v>133706585</v>
       </c>
       <c r="B14" t="n">
         <v>57975</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446792</v>
+        <v>446816</v>
       </c>
       <c r="R14" t="n">
-        <v>6997319</v>
+        <v>6997484</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133706577</v>
+        <v>133706587</v>
       </c>
       <c r="B15" t="n">
         <v>57975</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446838</v>
+        <v>446795</v>
       </c>
       <c r="R15" t="n">
-        <v>6997451</v>
+        <v>6997454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gammalt troligt bo av tretåig hackspett, ca 1,4m upp i tajgagrantickerötad granhögstubbe</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2198,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133706601</v>
+        <v>133706588</v>
       </c>
       <c r="B16" t="n">
         <v>57975</v>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446800</v>
+        <v>446805</v>
       </c>
       <c r="R16" t="n">
-        <v>6997283</v>
+        <v>6997442</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133706587</v>
+        <v>133706597</v>
       </c>
       <c r="B17" t="n">
         <v>57975</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446795</v>
+        <v>446792</v>
       </c>
       <c r="R17" t="n">
-        <v>6997454</v>
+        <v>6997319</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,7 +2422,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133706602</v>
+        <v>133706599</v>
       </c>
       <c r="B18" t="n">
         <v>57975</v>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446805</v>
+        <v>446796</v>
       </c>
       <c r="R18" t="n">
-        <v>6997283</v>
+        <v>6997286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,7 +2534,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133706588</v>
+        <v>133706601</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446805</v>
+        <v>446800</v>
       </c>
       <c r="R19" t="n">
-        <v>6997442</v>
+        <v>6997283</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,7 +2646,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133706585</v>
+        <v>133706602</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446816</v>
+        <v>446805</v>
       </c>
       <c r="R20" t="n">
-        <v>6997484</v>
+        <v>6997283</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2758,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133706606</v>
+        <v>133706603</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446774</v>
+        <v>446807</v>
       </c>
       <c r="R21" t="n">
-        <v>6997294</v>
+        <v>6997279</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,7 +2870,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133706607</v>
+        <v>133706604</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446894</v>
+        <v>446725</v>
       </c>
       <c r="R22" t="n">
-        <v>6997185</v>
+        <v>6997251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3094,7 +3094,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133706571</v>
+        <v>133706606</v>
       </c>
       <c r="B24" t="n">
         <v>57975</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446829</v>
+        <v>446774</v>
       </c>
       <c r="R24" t="n">
-        <v>6997424</v>
+        <v>6997294</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3206,7 +3206,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133706608</v>
+        <v>133706607</v>
       </c>
       <c r="B25" t="n">
         <v>57975</v>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446897</v>
+        <v>446894</v>
       </c>
       <c r="R25" t="n">
-        <v>6997181</v>
+        <v>6997185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133706561</v>
+        <v>133706608</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446865</v>
+        <v>446897</v>
       </c>
       <c r="R26" t="n">
-        <v>6997453</v>
+        <v>6997181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 56873-2025 artfynd.xlsx
+++ b/artfynd/A 56873-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706610</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706579</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706557</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706573</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706576</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706582</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706590</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706561</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706571</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1971,6 +2031,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706577</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706585</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706587</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,6 +2382,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706588</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2419,6 +2499,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706597</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2531,6 +2616,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706599</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2643,6 +2733,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706601</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2755,6 +2850,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706602</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2867,6 +2967,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706603</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2979,6 +3084,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706604</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3091,6 +3201,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706605</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3203,6 +3318,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706606</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3315,6 +3435,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706607</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3427,8 +3552,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706608</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>